--- a/data/WP18_sachgebiete_fraktionslos_zeitreihe.xlsx
+++ b/data/WP18_sachgebiete_fraktionslos_zeitreihe.xlsx
@@ -17,22 +17,22 @@
     <t xml:space="preserve">periode</t>
   </si>
   <si>
-    <t xml:space="preserve">Sachgebiet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anzahl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zeit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verspätet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pünktlichkeitsquote</t>
+    <t xml:space="preserve">Sachgebiet_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anzahl_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sachgebiet_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anzahl_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sachgebiet_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anzahl_3</t>
   </si>
   <si>
     <t xml:space="preserve">Klima</t>
@@ -413,112 +413,39 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
-      </c>
-      <c r="D2" t="n">
         <v>1</v>
       </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
       <c r="E2" t="n">
-        <v>22</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45078</v>
+        <v>45170</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
-      </c>
-      <c r="D3" t="n">
         <v>1</v>
       </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
       <c r="E3" t="n">
-        <v>27</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>45078</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="n">
-        <v>18</v>
-      </c>
-      <c r="D4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" t="n">
-        <v>27</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>45170</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="n">
-        <v>18</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>37</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>45170</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" t="n">
-        <v>18</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>37</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
+      <c r="F3"/>
+      <c r="G3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -754,13 +681,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25E9D836-3D5A-49FB-A1AD-D13307636E4F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFBBD25D-BC67-48B9-9A93-E542BC5DC5A6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B66D6D0-C58D-486E-9AF3-3B7DF5BEBFEE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52A6D194-5697-4C4D-B4DF-AAE1A51B97B4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D703A426-048A-4CA3-87D5-9F80380EC6CB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00C7AEE9-D731-438C-810C-81D67DE6518D}"/>
 </file>